--- a/허브누리_레시피_목록_상세_p1of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p1of6_썸네일.xlsx
@@ -30135,7 +30135,7 @@
         </is>
       </c>
     </row>
-    <row r="250" ht="28.125" customHeight="1">
+    <row r="250" ht="31.875" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
         <is>
           <t>라벤더 베이비스킨(고보습)</t>
@@ -30179,7 +30179,16 @@
 사용량은 어른의 사용량의 1/2~1/3정도</t>
         </is>
       </c>
-      <c r="H250" s="7" t="n"/>
+      <c r="H250" s="7" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 용기 하나에 정제수만 계량합니다.
+2~4. 다른 용기에 올리브리퀴드, 천연비타민E 넣고 용기를 기울여서 라벤더에센셜오일, 만다린에센셜오일 분량의 방울을 떨어뜨리세요. 잘 섞어주세요. 워낙 적은 양이라 기울여서 조준한 후 에센셜오일을 떨어뜨려주시면 잘 섞을 수 있어요.
+5. 잘 섞어주셔야 워터와 섞인 후 오일이 뜨지 않습니다.
+6~8. 1번 워터를 2번 오일류에다 붓고 많~~이 저어주고, 붓고 많~~이 저어주고 (한꺼번에 부어주시면 의외로 잘 섞이지도 않고 골고루 섞이는데 시간이 걸려요.)
+9~11. 잘 섞어준 다음 감초추출물과 수용성천연방부제, 글리세린을 계량하시고 섞어주세요. 용기에 부어주시면 완성^^</t>
+        </is>
+      </c>
       <c r="I250" s="7" t="n"/>
       <c r="J250" s="6" t="inlineStr">
         <is>
@@ -30187,7 +30196,7 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="28.125" customHeight="1">
+    <row r="251" ht="31.875" customHeight="1">
       <c r="A251" s="8" t="n"/>
       <c r="B251" s="8" t="inlineStr">
         <is>
@@ -30219,7 +30228,7 @@
       <c r="I251" s="8" t="n"/>
       <c r="J251" s="8" t="n"/>
     </row>
-    <row r="252" ht="28.125" customHeight="1">
+    <row r="252" ht="31.875" customHeight="1">
       <c r="A252" s="8" t="n"/>
       <c r="B252" s="8" t="inlineStr">
         <is>
@@ -30251,7 +30260,7 @@
       <c r="I252" s="8" t="n"/>
       <c r="J252" s="8" t="n"/>
     </row>
-    <row r="253" ht="28.125" customHeight="1">
+    <row r="253" ht="31.875" customHeight="1">
       <c r="A253" s="8" t="n"/>
       <c r="B253" s="8" t="n"/>
       <c r="C253" s="8" t="inlineStr">
@@ -30279,7 +30288,7 @@
       <c r="I253" s="8" t="n"/>
       <c r="J253" s="8" t="n"/>
     </row>
-    <row r="254" ht="28.125" customHeight="1">
+    <row r="254" ht="31.875" customHeight="1">
       <c r="A254" s="8" t="n"/>
       <c r="B254" s="8" t="n"/>
       <c r="C254" s="8" t="inlineStr">
@@ -30307,7 +30316,7 @@
       <c r="I254" s="8" t="n"/>
       <c r="J254" s="8" t="n"/>
     </row>
-    <row r="255" ht="28.125" customHeight="1">
+    <row r="255" ht="31.875" customHeight="1">
       <c r="A255" s="8" t="n"/>
       <c r="B255" s="8" t="inlineStr">
         <is>
@@ -30339,7 +30348,7 @@
       <c r="I255" s="8" t="n"/>
       <c r="J255" s="8" t="n"/>
     </row>
-    <row r="256" ht="28.125" customHeight="1">
+    <row r="256" ht="31.875" customHeight="1">
       <c r="A256" s="8" t="n"/>
       <c r="B256" s="8" t="n"/>
       <c r="C256" s="8" t="inlineStr">
@@ -30367,7 +30376,7 @@
       <c r="I256" s="8" t="n"/>
       <c r="J256" s="8" t="n"/>
     </row>
-    <row r="257" ht="28.125" customHeight="1">
+    <row r="257" ht="31.875" customHeight="1">
       <c r="A257" s="8" t="n"/>
       <c r="B257" s="8" t="n"/>
       <c r="C257" s="8" t="inlineStr">
